--- a/main/04_data_extraction/data_extracted_reading.xlsx
+++ b/main/04_data_extraction/data_extracted_reading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\orincon\scoping-ml-wave-seismology\main\04_data_extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDE920E-A438-461B-BFC5-C8B7F4374553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738BD2D6-A53A-4A5A-AA2F-F0075EE3740E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DAAC98F7-3F84-4A67-9EEA-E9091C806990}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
   <si>
     <t>Publication</t>
   </si>
@@ -225,13 +225,43 @@
     <t>1D</t>
   </si>
   <si>
-    <t>Multi-layer Perceptron regressor</t>
-  </si>
-  <si>
     <t>Encoder-decoder</t>
   </si>
   <si>
-    <t>CNN-based encoder–decoder</t>
+    <t>Convolutional neural network-based encoder–decoder</t>
+  </si>
+  <si>
+    <t>Poroelastic</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-layer Perceptron </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2D </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Finite-difference</t>
+  </si>
+  <si>
+    <t>SWINet</t>
+  </si>
+  <si>
+    <t>HydrogenNet (a hybrid 2D CNN hibrid fully-connected DNN).</t>
+  </si>
+  <si>
+    <t>Local plane-wave</t>
+  </si>
+  <si>
+    <t>Physics-informed neural network</t>
+  </si>
+  <si>
+    <t>CNN encoder–decoder</t>
+  </si>
+  <si>
+    <t>Revisar no parece ser problema inverso</t>
   </si>
 </sst>
 </file>
@@ -247,12 +277,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -267,8 +303,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,11 +620,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F743B1E8-28A3-4123-BEAB-42835B5F167D}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
@@ -698,6 +735,21 @@
       <c r="A15" t="s">
         <v>19</v>
       </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -719,22 +771,22 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -742,7 +794,7 @@
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
         <v>61</v>
@@ -754,7 +806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -762,7 +814,7 @@
         <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
         <v>55</v>
@@ -774,42 +826,90 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -817,7 +917,7 @@
         <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
         <v>61</v>
@@ -829,7 +929,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -849,12 +949,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
